--- a/src/adapter/etl-adapter-excel/tests/Flow/ETL/Adapter/Excel/Tests/Fixtures/orders_1k.xlsx
+++ b/src/adapter/etl-adapter-excel/tests/Flow/ETL/Adapter/Excel/Tests/Fixtures/orders_1k.xlsx
@@ -128,10 +128,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E2" s="0">
+        <v>24.4</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
@@ -173,9 +171,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E3" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
           <t>user-1@example.com</t>
@@ -216,11 +211,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
           <t>user-2@example.com</t>
@@ -261,14 +251,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E5" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
           <t>user-3@example.com</t>
@@ -309,11 +291,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E6" s="0">
         <v>24.4</v>
       </c>
@@ -357,11 +334,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
           <t>user-5@example.com</t>
@@ -402,6 +374,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
           <t>user-6@example.com</t>
@@ -482,9 +459,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E10" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
           <t>user-8@example.com</t>
@@ -525,11 +499,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
           <t>user-9@example.com</t>
@@ -570,8 +539,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E12" s="0">
-        <v>24.4</v>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -653,6 +624,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E14" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
           <t>user-12@example.com</t>
@@ -693,6 +672,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E15" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
           <t>user-13@example.com</t>
@@ -738,6 +725,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E16" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
           <t>user-14@example.com</t>
@@ -778,10 +768,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E17" s="0">
+        <v>24.4</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -823,14 +811,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E18" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
           <t>user-16@example.com</t>
@@ -871,8 +851,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E19" s="0">
-        <v>24.4</v>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -914,11 +896,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E20" s="0">
         <v>24.4</v>
       </c>
@@ -962,9 +939,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E21" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
           <t>user-19@example.com</t>
@@ -1005,14 +979,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E22" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
           <t>user-20@example.com</t>
@@ -1053,8 +1019,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E23" s="0">
-        <v>24.4</v>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1096,6 +1064,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E24" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
           <t>user-22@example.com</t>
@@ -1136,6 +1107,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E25" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
           <t>user-23@example.com</t>
@@ -1181,9 +1155,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E26" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
           <t>user-24@example.com</t>
@@ -1362,6 +1333,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E30" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
           <t>user-28@example.com</t>
@@ -1402,9 +1376,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E31" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
           <t>user-29@example.com</t>
@@ -1490,6 +1461,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E33" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
           <t>user-31@example.com</t>
@@ -1530,9 +1504,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E34" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
           <t>user-32@example.com</t>
@@ -1573,11 +1544,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E35" s="0">
         <v>24.4</v>
       </c>
@@ -1621,14 +1587,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E36" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
           <t>user-34@example.com</t>
@@ -1722,9 +1680,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E38" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
           <t>user-36@example.com</t>
@@ -1765,11 +1720,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E39" s="0">
         <v>24.4</v>
       </c>
@@ -1858,10 +1808,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E41" s="0">
+        <v>24.4</v>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
@@ -1951,11 +1899,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
           <t>user-41@example.com</t>
@@ -2001,6 +1944,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E44" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
           <t>user-42@example.com</t>
@@ -2041,6 +1987,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E45" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
           <t>user-43@example.com</t>
@@ -2081,6 +2030,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E46" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
           <t>user-44@example.com</t>
@@ -2161,8 +2118,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E48" s="0">
-        <v>24.4</v>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
@@ -2204,14 +2163,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D49" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E49" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
           <t>user-47@example.com</t>
@@ -2337,6 +2288,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E52" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
           <t>user-50@example.com</t>
@@ -2377,6 +2336,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
           <t>user-51@example.com</t>
@@ -2417,6 +2381,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
           <t>user-52@example.com</t>
@@ -2497,8 +2466,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E56" s="0">
-        <v>24.4</v>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
@@ -2540,14 +2511,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D57" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E57" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
           <t>user-55@example.com</t>
@@ -2588,11 +2551,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D58" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E58" s="0">
         <v>24.4</v>
       </c>
@@ -2636,11 +2594,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D59" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E59" s="0">
         <v>24.4</v>
       </c>
@@ -2684,9 +2637,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E60" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
           <t>user-58@example.com</t>
@@ -2727,14 +2677,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D61" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E61" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
           <t>user-59@example.com</t>
@@ -2775,11 +2717,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D62" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
           <t>user-60@example.com</t>
@@ -2820,6 +2757,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E63" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
           <t>user-61@example.com</t>
@@ -2860,11 +2805,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
           <t>user-62@example.com</t>
@@ -2985,6 +2925,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E67" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
           <t>user-65@example.com</t>
@@ -3065,14 +3008,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D69" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E69" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
           <t>user-67@example.com</t>
@@ -3113,9 +3048,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E70" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
           <t>user-68@example.com</t>
@@ -3156,6 +3088,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E71" s="0">
         <v>24.4</v>
       </c>
@@ -3199,6 +3136,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
           <t>user-70@example.com</t>
@@ -3239,11 +3181,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D73" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
           <t>user-71@example.com</t>
@@ -3284,9 +3221,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E74" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
           <t>user-72@example.com</t>
@@ -3327,6 +3261,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E75" s="0">
         <v>24.4</v>
       </c>
@@ -3410,8 +3349,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E77" s="0">
-        <v>24.4</v>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
@@ -3453,11 +3394,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D78" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E78" s="0">
         <v>24.4</v>
       </c>
@@ -3501,11 +3437,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D79" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
           <t>user-77@example.com</t>
@@ -3546,9 +3477,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E80" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
           <t>user-78@example.com</t>
@@ -3594,6 +3522,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E81" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
           <t>user-79@example.com</t>
@@ -3677,11 +3608,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D83" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E83" s="0">
         <v>24.4</v>
       </c>
@@ -3725,9 +3651,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E84" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
           <t>user-82@example.com</t>
@@ -3768,11 +3691,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D85" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
           <t>user-83@example.com</t>
@@ -3813,6 +3731,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E86" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
           <t>user-84@example.com</t>
@@ -3853,11 +3774,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D87" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E87" s="0">
         <v>24.4</v>
       </c>
@@ -3901,11 +3817,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D88" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
           <t>user-86@example.com</t>
@@ -4029,11 +3940,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D91" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
           <t>user-89@example.com</t>
@@ -4210,11 +4116,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D95" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E95" s="0">
         <v>24.4</v>
       </c>
@@ -4258,6 +4159,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
           <t>user-94@example.com</t>
@@ -4298,6 +4204,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E97" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
           <t>user-95@example.com</t>
@@ -4343,9 +4252,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E98" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
           <t>user-96@example.com</t>
@@ -4391,6 +4297,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E99" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
           <t>user-97@example.com</t>
@@ -4476,6 +4385,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E101" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
           <t>user-99@example.com</t>
@@ -4521,9 +4433,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E102" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
           <t>user-100@example.com</t>
@@ -4564,6 +4473,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E103" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
           <t>user-101@example.com</t>
@@ -4740,14 +4657,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D107" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E107" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F107" s="0" t="inlineStr">
         <is>
           <t>user-105@example.com</t>
@@ -4788,14 +4697,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D108" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E108" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F108" s="0" t="inlineStr">
         <is>
           <t>user-106@example.com</t>
@@ -4836,8 +4737,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E109" s="0">
-        <v>24.4</v>
+      <c r="D109" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
@@ -4879,14 +4782,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D110" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E110" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F110" s="0" t="inlineStr">
         <is>
           <t>user-108@example.com</t>
@@ -4932,6 +4827,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E111" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F111" s="0" t="inlineStr">
         <is>
           <t>user-109@example.com</t>
@@ -5012,11 +4910,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D113" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
           <t>user-111@example.com</t>
@@ -5062,6 +4955,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E114" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
           <t>user-112@example.com</t>
@@ -5102,8 +4998,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E115" s="0">
-        <v>24.4</v>
+      <c r="D115" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
@@ -5145,11 +5043,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D116" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E116" s="0">
         <v>24.4</v>
       </c>
@@ -5281,6 +5174,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D119" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E119" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F119" s="0" t="inlineStr">
         <is>
           <t>user-117@example.com</t>
@@ -5326,6 +5227,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E120" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F120" s="0" t="inlineStr">
         <is>
           <t>user-118@example.com</t>
@@ -5366,6 +5270,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E121" s="0">
         <v>24.4</v>
       </c>
@@ -5409,6 +5318,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E122" s="0">
         <v>24.4</v>
       </c>
@@ -5452,14 +5366,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D123" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E123" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
           <t>user-121@example.com</t>
@@ -5500,11 +5406,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D124" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E124" s="0">
         <v>24.4</v>
       </c>
@@ -5548,14 +5449,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D125" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E125" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
           <t>user-123@example.com</t>
@@ -5641,11 +5534,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D127" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E127" s="0">
         <v>24.4</v>
       </c>
@@ -5729,8 +5617,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E129" s="0">
-        <v>24.4</v>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
@@ -5820,6 +5710,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
           <t>user-129@example.com</t>
@@ -5865,9 +5760,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E132" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
           <t>user-130@example.com</t>
@@ -5908,11 +5800,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D133" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E133" s="0">
         <v>24.4</v>
       </c>
@@ -5956,14 +5843,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D134" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E134" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
           <t>user-132@example.com</t>
@@ -6004,6 +5883,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
           <t>user-133@example.com</t>
@@ -6044,6 +5928,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E136" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
           <t>user-134@example.com</t>
@@ -6084,6 +5976,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
           <t>user-135@example.com</t>
@@ -6129,6 +6026,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E138" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F138" s="0" t="inlineStr">
         <is>
           <t>user-136@example.com</t>
@@ -6169,8 +6069,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E139" s="0">
-        <v>24.4</v>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
@@ -6212,9 +6114,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E140" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F140" s="0" t="inlineStr">
         <is>
           <t>user-138@example.com</t>
@@ -6255,14 +6154,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D141" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E141" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F141" s="0" t="inlineStr">
         <is>
           <t>user-139@example.com</t>
@@ -6394,6 +6285,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E144" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
           <t>user-142@example.com</t>
@@ -6434,14 +6328,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D145" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E145" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F145" s="0" t="inlineStr">
         <is>
           <t>user-143@example.com</t>
@@ -6482,6 +6368,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D146" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
           <t>user-144@example.com</t>
@@ -6522,6 +6413,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E147" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F147" s="0" t="inlineStr">
         <is>
           <t>user-145@example.com</t>
@@ -6562,6 +6461,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E148" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F148" s="0" t="inlineStr">
         <is>
           <t>user-146@example.com</t>
@@ -6602,11 +6504,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D149" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
           <t>user-147@example.com</t>
@@ -6647,11 +6544,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D150" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
           <t>user-148@example.com</t>
@@ -6692,11 +6584,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D151" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F151" s="0" t="inlineStr">
         <is>
           <t>user-149@example.com</t>
@@ -6737,6 +6624,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E152" s="0">
         <v>24.4</v>
       </c>
@@ -6780,6 +6672,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E153" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F153" s="0" t="inlineStr">
         <is>
           <t>user-151@example.com</t>
@@ -6820,6 +6720,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E154" s="0">
         <v>24.4</v>
       </c>
@@ -6911,14 +6816,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D156" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E156" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
           <t>user-154@example.com</t>
@@ -7012,9 +6909,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E158" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F158" s="0" t="inlineStr">
         <is>
           <t>user-156@example.com</t>
@@ -7055,6 +6949,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E159" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F159" s="0" t="inlineStr">
         <is>
           <t>user-157@example.com</t>
@@ -7180,6 +7082,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E162" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F162" s="0" t="inlineStr">
         <is>
           <t>user-160@example.com</t>
@@ -7220,9 +7130,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E163" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F163" s="0" t="inlineStr">
         <is>
           <t>user-161@example.com</t>
@@ -7263,14 +7170,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D164" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E164" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F164" s="0" t="inlineStr">
         <is>
           <t>user-162@example.com</t>
@@ -7311,11 +7210,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D165" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E165" s="0">
         <v>24.4</v>
       </c>
@@ -7359,6 +7253,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E166" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F166" s="0" t="inlineStr">
         <is>
           <t>user-164@example.com</t>
@@ -7399,14 +7296,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D167" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E167" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F167" s="0" t="inlineStr">
         <is>
           <t>user-165@example.com</t>
@@ -7447,8 +7336,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E168" s="0">
-        <v>24.4</v>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F168" s="0" t="inlineStr">
         <is>
@@ -7495,9 +7386,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E169" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F169" s="0" t="inlineStr">
         <is>
           <t>user-167@example.com</t>
@@ -7581,6 +7469,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E171" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F171" s="0" t="inlineStr">
         <is>
           <t>user-169@example.com</t>
@@ -7621,8 +7512,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E172" s="0">
-        <v>24.4</v>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F172" s="0" t="inlineStr">
         <is>
@@ -7669,6 +7562,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E173" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F173" s="0" t="inlineStr">
         <is>
           <t>user-171@example.com</t>
@@ -7749,11 +7645,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D175" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F175" s="0" t="inlineStr">
         <is>
           <t>user-173@example.com</t>
@@ -7799,6 +7690,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E176" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F176" s="0" t="inlineStr">
         <is>
           <t>user-174@example.com</t>
@@ -7839,10 +7733,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D177" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E177" s="0">
+        <v>24.4</v>
       </c>
       <c r="F177" s="0" t="inlineStr">
         <is>
@@ -7884,6 +7776,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E178" s="0">
         <v>24.4</v>
       </c>
@@ -7927,14 +7824,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D179" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E179" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F179" s="0" t="inlineStr">
         <is>
           <t>user-177@example.com</t>
@@ -7975,6 +7864,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E180" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F180" s="0" t="inlineStr">
         <is>
           <t>user-178@example.com</t>
@@ -8068,9 +7960,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E182" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F182" s="0" t="inlineStr">
         <is>
           <t>user-180@example.com</t>
@@ -8111,6 +8000,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E183" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F183" s="0" t="inlineStr">
         <is>
           <t>user-181@example.com</t>
@@ -8201,9 +8093,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E185" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F185" s="0" t="inlineStr">
         <is>
           <t>user-183@example.com</t>
@@ -8284,11 +8173,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D187" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E187" s="0">
         <v>24.4</v>
       </c>
@@ -8332,6 +8216,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E188" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F188" s="0" t="inlineStr">
         <is>
           <t>user-186@example.com</t>
@@ -8415,11 +8302,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D190" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F190" s="0" t="inlineStr">
         <is>
           <t>user-188@example.com</t>
@@ -8460,6 +8342,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E191" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F191" s="0" t="inlineStr">
         <is>
           <t>user-189@example.com</t>
@@ -8500,6 +8390,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E192" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F192" s="0" t="inlineStr">
         <is>
           <t>user-190@example.com</t>
@@ -8585,11 +8483,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D194" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E194" s="0">
         <v>24.4</v>
       </c>
@@ -8633,6 +8526,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E195" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F195" s="0" t="inlineStr">
         <is>
           <t>user-193@example.com</t>
@@ -8713,6 +8614,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D197" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E197" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F197" s="0" t="inlineStr">
         <is>
           <t>user-195@example.com</t>
@@ -8753,8 +8662,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E198" s="0">
-        <v>24.4</v>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F198" s="0" t="inlineStr">
         <is>
@@ -8796,6 +8707,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F199" s="0" t="inlineStr">
         <is>
           <t>user-197@example.com</t>
@@ -8836,6 +8752,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E200" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F200" s="0" t="inlineStr">
         <is>
           <t>user-198@example.com</t>
@@ -8919,10 +8838,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D202" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E202" s="0">
+        <v>24.4</v>
       </c>
       <c r="F202" s="0" t="inlineStr">
         <is>
@@ -8964,14 +8881,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D203" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E203" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F203" s="0" t="inlineStr">
         <is>
           <t>user-201@example.com</t>
@@ -9012,11 +8921,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D204" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E204" s="0">
         <v>24.4</v>
       </c>
@@ -9103,6 +9007,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E206" s="0">
         <v>24.4</v>
       </c>
@@ -9146,11 +9055,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D207" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F207" s="0" t="inlineStr">
         <is>
           <t>user-205@example.com</t>
@@ -9191,6 +9095,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E208" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F208" s="0" t="inlineStr">
         <is>
           <t>user-206@example.com</t>
@@ -9231,11 +9143,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D209" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E209" s="0">
         <v>24.4</v>
       </c>
@@ -9279,6 +9186,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E210" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F210" s="0" t="inlineStr">
         <is>
           <t>user-208@example.com</t>
@@ -9319,6 +9234,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E211" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F211" s="0" t="inlineStr">
         <is>
           <t>user-209@example.com</t>
@@ -9364,9 +9282,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E212" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F212" s="0" t="inlineStr">
         <is>
           <t>user-210@example.com</t>
@@ -9447,6 +9362,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E214" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F214" s="0" t="inlineStr">
         <is>
           <t>user-212@example.com</t>
@@ -9487,9 +9405,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E215" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F215" s="0" t="inlineStr">
         <is>
           <t>user-213@example.com</t>
@@ -9530,6 +9445,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E216" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F216" s="0" t="inlineStr">
         <is>
           <t>user-214@example.com</t>
@@ -9570,8 +9488,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E217" s="0">
-        <v>24.4</v>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F217" s="0" t="inlineStr">
         <is>
@@ -9618,9 +9538,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E218" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F218" s="0" t="inlineStr">
         <is>
           <t>user-216@example.com</t>
@@ -9749,14 +9666,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D221" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E221" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F221" s="0" t="inlineStr">
         <is>
           <t>user-219@example.com</t>
@@ -9797,11 +9706,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D222" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E222" s="0">
         <v>24.4</v>
       </c>
@@ -9845,6 +9749,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E223" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F223" s="0" t="inlineStr">
         <is>
           <t>user-221@example.com</t>
@@ -9885,6 +9792,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E224" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F224" s="0" t="inlineStr">
         <is>
           <t>user-222@example.com</t>
@@ -10016,9 +9926,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E227" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F227" s="0" t="inlineStr">
         <is>
           <t>user-225@example.com</t>
@@ -10059,11 +9966,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D228" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F228" s="0" t="inlineStr">
         <is>
           <t>user-226@example.com</t>
@@ -10104,8 +10006,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E229" s="0">
-        <v>24.4</v>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F229" s="0" t="inlineStr">
         <is>
@@ -10147,6 +10051,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F230" s="0" t="inlineStr">
         <is>
           <t>user-228@example.com</t>
@@ -10230,9 +10139,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E232" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F232" s="0" t="inlineStr">
         <is>
           <t>user-230@example.com</t>
@@ -10321,14 +10227,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D234" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E234" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F234" s="0" t="inlineStr">
         <is>
           <t>user-232@example.com</t>
@@ -10369,10 +10267,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D235" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E235" s="0">
+        <v>24.4</v>
       </c>
       <c r="F235" s="0" t="inlineStr">
         <is>
@@ -10414,11 +10310,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D236" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E236" s="0">
         <v>24.4</v>
       </c>
@@ -10462,11 +10353,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D237" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F237" s="0" t="inlineStr">
         <is>
           <t>user-235@example.com</t>
@@ -10550,6 +10436,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E239" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F239" s="0" t="inlineStr">
         <is>
           <t>user-237@example.com</t>
@@ -10590,8 +10479,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E240" s="0">
-        <v>24.4</v>
+      <c r="D240" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F240" s="0" t="inlineStr">
         <is>
@@ -10678,10 +10569,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D242" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E242" s="0">
+        <v>24.4</v>
       </c>
       <c r="F242" s="0" t="inlineStr">
         <is>
@@ -10723,11 +10612,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D243" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F243" s="0" t="inlineStr">
         <is>
           <t>user-241@example.com</t>
@@ -10816,11 +10700,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D245" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F245" s="0" t="inlineStr">
         <is>
           <t>user-243@example.com</t>
@@ -10901,11 +10780,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D247" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F247" s="0" t="inlineStr">
         <is>
           <t>user-245@example.com</t>
@@ -10946,6 +10820,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F248" s="0" t="inlineStr">
         <is>
           <t>user-246@example.com</t>
@@ -10991,6 +10870,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E249" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F249" s="0" t="inlineStr">
         <is>
           <t>user-247@example.com</t>
@@ -11036,6 +10918,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E250" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F250" s="0" t="inlineStr">
         <is>
           <t>user-248@example.com</t>
@@ -11076,11 +10961,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D251" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E251" s="0">
         <v>24.4</v>
       </c>
@@ -11124,10 +11004,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D252" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E252" s="0">
+        <v>24.4</v>
       </c>
       <c r="F252" s="0" t="inlineStr">
         <is>
@@ -11174,6 +11052,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E253" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F253" s="0" t="inlineStr">
         <is>
           <t>user-251@example.com</t>
@@ -11214,6 +11095,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E254" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F254" s="0" t="inlineStr">
         <is>
           <t>user-252@example.com</t>
@@ -11254,11 +11138,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D255" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E255" s="0">
         <v>24.4</v>
       </c>
@@ -11307,9 +11186,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E256" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F256" s="0" t="inlineStr">
         <is>
           <t>user-254@example.com</t>
@@ -11355,6 +11231,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E257" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F257" s="0" t="inlineStr">
         <is>
           <t>user-255@example.com</t>
@@ -11395,6 +11274,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D258" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F258" s="0" t="inlineStr">
         <is>
           <t>user-256@example.com</t>
@@ -11435,6 +11319,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D259" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F259" s="0" t="inlineStr">
         <is>
           <t>user-257@example.com</t>
@@ -11475,6 +11364,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D260" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E260" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F260" s="0" t="inlineStr">
         <is>
           <t>user-258@example.com</t>
@@ -11520,6 +11417,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E261" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F261" s="0" t="inlineStr">
         <is>
           <t>user-259@example.com</t>
@@ -11560,14 +11460,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D262" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E262" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F262" s="0" t="inlineStr">
         <is>
           <t>user-260@example.com</t>
@@ -11656,11 +11548,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D264" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E264" s="0">
         <v>24.4</v>
       </c>
@@ -11704,6 +11591,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D265" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E265" s="0">
         <v>24.4</v>
       </c>
@@ -11792,6 +11684,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E267" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F267" s="0" t="inlineStr">
         <is>
           <t>user-265@example.com</t>
@@ -11877,11 +11772,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D269" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E269" s="0">
         <v>24.4</v>
       </c>
@@ -11970,11 +11860,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D271" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E271" s="0">
         <v>24.4</v>
       </c>
@@ -12018,6 +11903,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D272" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F272" s="0" t="inlineStr">
         <is>
           <t>user-270@example.com</t>
@@ -12154,6 +12044,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D275" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E275" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F275" s="0" t="inlineStr">
         <is>
           <t>user-273@example.com</t>
@@ -12194,6 +12092,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D276" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F276" s="0" t="inlineStr">
         <is>
           <t>user-274@example.com</t>
@@ -12239,9 +12142,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E277" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F277" s="0" t="inlineStr">
         <is>
           <t>user-275@example.com</t>
@@ -12282,11 +12182,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D278" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F278" s="0" t="inlineStr">
         <is>
           <t>user-276@example.com</t>
@@ -12327,9 +12222,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E279" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F279" s="0" t="inlineStr">
         <is>
           <t>user-277@example.com</t>
@@ -12370,8 +12262,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E280" s="0">
-        <v>24.4</v>
+      <c r="D280" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F280" s="0" t="inlineStr">
         <is>
@@ -12453,6 +12347,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D282" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E282" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F282" s="0" t="inlineStr">
         <is>
           <t>user-280@example.com</t>
@@ -12493,11 +12395,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D283" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F283" s="0" t="inlineStr">
         <is>
           <t>user-281@example.com</t>
@@ -12543,9 +12440,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E284" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F284" s="0" t="inlineStr">
         <is>
           <t>user-282@example.com</t>
@@ -12586,10 +12480,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D285" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E285" s="0">
+        <v>24.4</v>
       </c>
       <c r="F285" s="0" t="inlineStr">
         <is>
@@ -12631,9 +12523,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E286" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F286" s="0" t="inlineStr">
         <is>
           <t>user-284@example.com</t>
@@ -12674,6 +12563,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E287" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F287" s="0" t="inlineStr">
         <is>
           <t>user-285@example.com</t>
@@ -12767,6 +12659,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E289" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F289" s="0" t="inlineStr">
         <is>
           <t>user-287@example.com</t>
@@ -12807,9 +12702,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E290" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F290" s="0" t="inlineStr">
         <is>
           <t>user-288@example.com</t>
@@ -12850,6 +12742,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E291" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F291" s="0" t="inlineStr">
         <is>
           <t>user-289@example.com</t>
@@ -12981,14 +12876,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D294" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E294" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F294" s="0" t="inlineStr">
         <is>
           <t>user-292@example.com</t>
@@ -13029,9 +12916,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E295" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F295" s="0" t="inlineStr">
         <is>
           <t>user-293@example.com</t>
@@ -13072,6 +12956,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D296" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E296" s="0">
         <v>24.4</v>
       </c>
@@ -13115,11 +13004,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D297" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F297" s="0" t="inlineStr">
         <is>
           <t>user-295@example.com</t>
@@ -13160,6 +13044,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D298" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F298" s="0" t="inlineStr">
         <is>
           <t>user-296@example.com</t>
@@ -13205,6 +13094,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E299" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F299" s="0" t="inlineStr">
         <is>
           <t>user-297@example.com</t>
@@ -13288,6 +13180,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D301" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F301" s="0" t="inlineStr">
         <is>
           <t>user-299@example.com</t>
@@ -13426,6 +13323,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E304" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F304" s="0" t="inlineStr">
         <is>
           <t>user-302@example.com</t>
@@ -13466,9 +13366,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E305" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F305" s="0" t="inlineStr">
         <is>
           <t>user-303@example.com</t>
@@ -13509,14 +13406,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D306" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E306" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F306" s="0" t="inlineStr">
         <is>
           <t>user-304@example.com</t>
@@ -13610,9 +13499,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E308" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F308" s="0" t="inlineStr">
         <is>
           <t>user-306@example.com</t>
@@ -13653,6 +13539,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D309" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E309" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F309" s="0" t="inlineStr">
         <is>
           <t>user-307@example.com</t>
@@ -13733,8 +13627,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E311" s="0">
-        <v>24.4</v>
+      <c r="D311" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F311" s="0" t="inlineStr">
         <is>
@@ -13816,11 +13712,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D313" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E313" s="0">
         <v>24.4</v>
       </c>
@@ -13864,6 +13755,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D314" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F314" s="0" t="inlineStr">
         <is>
           <t>user-312@example.com</t>
@@ -13909,6 +13805,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E315" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F315" s="0" t="inlineStr">
         <is>
           <t>user-313@example.com</t>
@@ -13949,14 +13848,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D316" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E316" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F316" s="0" t="inlineStr">
         <is>
           <t>user-314@example.com</t>
@@ -13997,10 +13888,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D317" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E317" s="0">
+        <v>24.4</v>
       </c>
       <c r="F317" s="0" t="inlineStr">
         <is>
@@ -14085,9 +13974,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E319" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F319" s="0" t="inlineStr">
         <is>
           <t>user-317@example.com</t>
@@ -14133,9 +14019,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E320" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F320" s="0" t="inlineStr">
         <is>
           <t>user-318@example.com</t>
@@ -14176,8 +14059,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E321" s="0">
-        <v>24.4</v>
+      <c r="D321" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F321" s="0" t="inlineStr">
         <is>
@@ -14259,6 +14144,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D323" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F323" s="0" t="inlineStr">
         <is>
           <t>user-321@example.com</t>
@@ -14299,6 +14189,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E324" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F324" s="0" t="inlineStr">
         <is>
           <t>user-322@example.com</t>
@@ -14379,9 +14272,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E326" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F326" s="0" t="inlineStr">
         <is>
           <t>user-324@example.com</t>
@@ -14422,11 +14312,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D327" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E327" s="0">
         <v>24.4</v>
       </c>
@@ -14470,6 +14355,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D328" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E328" s="0">
         <v>24.4</v>
       </c>
@@ -14513,9 +14403,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E329" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F329" s="0" t="inlineStr">
         <is>
           <t>user-327@example.com</t>
@@ -14561,6 +14448,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E330" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F330" s="0" t="inlineStr">
         <is>
           <t>user-328@example.com</t>
@@ -14601,6 +14491,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D331" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F331" s="0" t="inlineStr">
         <is>
           <t>user-329@example.com</t>
@@ -14641,6 +14536,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D332" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E332" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F332" s="0" t="inlineStr">
         <is>
           <t>user-330@example.com</t>
@@ -14681,8 +14584,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E333" s="0">
-        <v>24.4</v>
+      <c r="D333" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F333" s="0" t="inlineStr">
         <is>
@@ -14724,11 +14629,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D334" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F334" s="0" t="inlineStr">
         <is>
           <t>user-332@example.com</t>
@@ -14937,10 +14837,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D339" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E339" s="0">
+        <v>24.4</v>
       </c>
       <c r="F339" s="0" t="inlineStr">
         <is>
@@ -14982,9 +14880,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E340" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F340" s="0" t="inlineStr">
         <is>
           <t>user-338@example.com</t>
@@ -15025,9 +14920,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E341" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F341" s="0" t="inlineStr">
         <is>
           <t>user-339@example.com</t>
@@ -15068,8 +14960,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E342" s="0">
-        <v>24.4</v>
+      <c r="D342" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F342" s="0" t="inlineStr">
         <is>
@@ -15159,6 +15053,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D344" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E344" s="0">
         <v>24.4</v>
       </c>
@@ -15207,9 +15106,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E345" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F345" s="0" t="inlineStr">
         <is>
           <t>user-343@example.com</t>
@@ -15295,6 +15191,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D347" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E347" s="0">
         <v>24.4</v>
       </c>
@@ -15338,10 +15239,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D348" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E348" s="0">
+        <v>24.4</v>
       </c>
       <c r="F348" s="0" t="inlineStr">
         <is>
@@ -15426,10 +15325,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D350" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E350" s="0">
+        <v>24.4</v>
       </c>
       <c r="F350" s="0" t="inlineStr">
         <is>
@@ -15471,6 +15368,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E351" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F351" s="0" t="inlineStr">
         <is>
           <t>user-349@example.com</t>
@@ -15561,9 +15461,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E353" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F353" s="0" t="inlineStr">
         <is>
           <t>user-351@example.com</t>
@@ -15609,6 +15506,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E354" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F354" s="0" t="inlineStr">
         <is>
           <t>user-352@example.com</t>
@@ -15694,10 +15594,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D356" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E356" s="0">
+        <v>24.4</v>
       </c>
       <c r="F356" s="0" t="inlineStr">
         <is>
@@ -15784,11 +15682,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D358" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F358" s="0" t="inlineStr">
         <is>
           <t>user-356@example.com</t>
@@ -15829,11 +15722,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D359" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E359" s="0">
         <v>24.4</v>
       </c>
@@ -15877,9 +15765,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E360" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F360" s="0" t="inlineStr">
         <is>
           <t>user-358@example.com</t>
@@ -15920,6 +15805,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E361" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F361" s="0" t="inlineStr">
         <is>
           <t>user-359@example.com</t>
@@ -16130,11 +16018,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D366" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F366" s="0" t="inlineStr">
         <is>
           <t>user-364@example.com</t>
@@ -16175,11 +16058,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D367" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F367" s="0" t="inlineStr">
         <is>
           <t>user-365@example.com</t>
@@ -16220,11 +16098,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D368" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F368" s="0" t="inlineStr">
         <is>
           <t>user-366@example.com</t>
@@ -16313,14 +16186,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D370" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E370" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F370" s="0" t="inlineStr">
         <is>
           <t>user-368@example.com</t>
@@ -16361,11 +16226,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D371" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E371" s="0">
         <v>24.4</v>
       </c>
@@ -16414,6 +16274,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E372" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F372" s="0" t="inlineStr">
         <is>
           <t>user-370@example.com</t>
@@ -16454,14 +16317,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D373" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E373" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F373" s="0" t="inlineStr">
         <is>
           <t>user-371@example.com</t>
@@ -16600,6 +16455,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E376" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F376" s="0" t="inlineStr">
         <is>
           <t>user-374@example.com</t>
@@ -16640,11 +16498,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D377" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F377" s="0" t="inlineStr">
         <is>
           <t>user-375@example.com</t>
@@ -16725,14 +16578,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D379" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E379" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F379" s="0" t="inlineStr">
         <is>
           <t>user-377@example.com</t>
@@ -16773,9 +16618,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E380" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F380" s="0" t="inlineStr">
         <is>
           <t>user-378@example.com</t>
@@ -16816,6 +16658,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D381" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E381" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F381" s="0" t="inlineStr">
         <is>
           <t>user-379@example.com</t>
@@ -16856,6 +16706,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D382" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F382" s="0" t="inlineStr">
         <is>
           <t>user-380@example.com</t>
@@ -16901,9 +16756,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E383" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F383" s="0" t="inlineStr">
         <is>
           <t>user-381@example.com</t>
@@ -16949,9 +16801,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E384" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F384" s="0" t="inlineStr">
         <is>
           <t>user-382@example.com</t>
@@ -16992,10 +16841,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D385" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E385" s="0">
+        <v>24.4</v>
       </c>
       <c r="F385" s="0" t="inlineStr">
         <is>
@@ -17037,14 +16884,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D386" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E386" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F386" s="0" t="inlineStr">
         <is>
           <t>user-384@example.com</t>
@@ -17090,9 +16929,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E387" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F387" s="0" t="inlineStr">
         <is>
           <t>user-385@example.com</t>
@@ -17133,10 +16969,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D388" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E388" s="0">
+        <v>24.4</v>
       </c>
       <c r="F388" s="0" t="inlineStr">
         <is>
@@ -17178,6 +17012,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D389" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F389" s="0" t="inlineStr">
         <is>
           <t>user-387@example.com</t>
@@ -17218,6 +17057,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D390" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F390" s="0" t="inlineStr">
         <is>
           <t>user-388@example.com</t>
@@ -17258,14 +17102,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D391" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E391" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F391" s="0" t="inlineStr">
         <is>
           <t>user-389@example.com</t>
@@ -17351,11 +17187,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D393" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E393" s="0">
         <v>24.4</v>
       </c>
@@ -17399,10 +17230,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D394" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E394" s="0">
+        <v>24.4</v>
       </c>
       <c r="F394" s="0" t="inlineStr">
         <is>
@@ -17532,6 +17361,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E397" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F397" s="0" t="inlineStr">
         <is>
           <t>user-395@example.com</t>
@@ -17572,11 +17404,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D398" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F398" s="0" t="inlineStr">
         <is>
           <t>user-396@example.com</t>
@@ -17622,6 +17449,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E399" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F399" s="0" t="inlineStr">
         <is>
           <t>user-397@example.com</t>
@@ -17662,6 +17492,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D400" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E400" s="0">
         <v>24.4</v>
       </c>
@@ -17705,14 +17540,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D401" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E401" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F401" s="0" t="inlineStr">
         <is>
           <t>user-399@example.com</t>
@@ -17753,14 +17580,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D402" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E402" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F402" s="0" t="inlineStr">
         <is>
           <t>user-400@example.com</t>
@@ -17806,9 +17625,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E403" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F403" s="0" t="inlineStr">
         <is>
           <t>user-401@example.com</t>
@@ -17849,11 +17665,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D404" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E404" s="0">
         <v>24.4</v>
       </c>
@@ -17897,11 +17708,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D405" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F405" s="0" t="inlineStr">
         <is>
           <t>user-403@example.com</t>
@@ -17942,10 +17748,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D406" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E406" s="0">
+        <v>24.4</v>
       </c>
       <c r="F406" s="0" t="inlineStr">
         <is>
@@ -18040,9 +17844,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E408" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F408" s="0" t="inlineStr">
         <is>
           <t>user-406@example.com</t>
@@ -18083,6 +17884,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D409" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E409" s="0">
         <v>24.4</v>
       </c>
@@ -18126,10 +17932,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D410" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E410" s="0">
+        <v>24.4</v>
       </c>
       <c r="F410" s="0" t="inlineStr">
         <is>
@@ -18171,6 +17975,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D411" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F411" s="0" t="inlineStr">
         <is>
           <t>user-409@example.com</t>
@@ -18211,11 +18020,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D412" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E412" s="0">
         <v>24.4</v>
       </c>
@@ -18299,6 +18103,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E414" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F414" s="0" t="inlineStr">
         <is>
           <t>user-412@example.com</t>
@@ -18339,10 +18151,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D415" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E415" s="0">
+        <v>24.4</v>
       </c>
       <c r="F415" s="0" t="inlineStr">
         <is>
@@ -18384,6 +18194,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D416" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E416" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F416" s="0" t="inlineStr">
         <is>
           <t>user-414@example.com</t>
@@ -18469,14 +18287,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D418" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E418" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F418" s="0" t="inlineStr">
         <is>
           <t>user-416@example.com</t>
@@ -18517,14 +18327,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D419" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E419" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F419" s="0" t="inlineStr">
         <is>
           <t>user-417@example.com</t>
@@ -18565,6 +18367,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D420" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F420" s="0" t="inlineStr">
         <is>
           <t>user-418@example.com</t>
@@ -18605,14 +18412,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D421" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E421" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F421" s="0" t="inlineStr">
         <is>
           <t>user-419@example.com</t>
@@ -18653,6 +18452,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D422" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E422" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F422" s="0" t="inlineStr">
         <is>
           <t>user-420@example.com</t>
@@ -18693,11 +18500,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D423" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F423" s="0" t="inlineStr">
         <is>
           <t>user-421@example.com</t>
@@ -18738,11 +18540,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D424" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E424" s="0">
         <v>24.4</v>
       </c>
@@ -18791,9 +18588,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E425" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F425" s="0" t="inlineStr">
         <is>
           <t>user-423@example.com</t>
@@ -18834,6 +18628,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E426" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F426" s="0" t="inlineStr">
         <is>
           <t>user-424@example.com</t>
@@ -18917,9 +18714,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E428" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F428" s="0" t="inlineStr">
         <is>
           <t>user-426@example.com</t>
@@ -18960,11 +18754,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D429" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F429" s="0" t="inlineStr">
         <is>
           <t>user-427@example.com</t>
@@ -19005,9 +18794,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E430" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F430" s="0" t="inlineStr">
         <is>
           <t>user-428@example.com</t>
@@ -19053,6 +18839,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E431" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F431" s="0" t="inlineStr">
         <is>
           <t>user-429@example.com</t>
@@ -19093,6 +18882,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E432" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F432" s="0" t="inlineStr">
         <is>
           <t>user-430@example.com</t>
@@ -19133,11 +18925,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D433" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E433" s="0">
         <v>24.4</v>
       </c>
@@ -19181,6 +18968,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D434" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E434" s="0">
         <v>24.4</v>
       </c>
@@ -19269,6 +19061,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D436" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E436" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F436" s="0" t="inlineStr">
         <is>
           <t>user-434@example.com</t>
@@ -19352,8 +19152,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E438" s="0">
-        <v>24.4</v>
+      <c r="D438" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F438" s="0" t="inlineStr">
         <is>
@@ -19395,6 +19197,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D439" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E439" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F439" s="0" t="inlineStr">
         <is>
           <t>user-437@example.com</t>
@@ -19435,6 +19245,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D440" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E440" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F440" s="0" t="inlineStr">
         <is>
           <t>user-438@example.com</t>
@@ -19475,10 +19293,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D441" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E441" s="0">
+        <v>24.4</v>
       </c>
       <c r="F441" s="0" t="inlineStr">
         <is>
@@ -19560,9 +19376,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E443" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F443" s="0" t="inlineStr">
         <is>
           <t>user-441@example.com</t>
@@ -19603,6 +19416,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E444" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F444" s="0" t="inlineStr">
         <is>
           <t>user-442@example.com</t>
@@ -19643,11 +19459,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D445" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E445" s="0">
         <v>24.4</v>
       </c>
@@ -19691,6 +19502,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E446" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F446" s="0" t="inlineStr">
         <is>
           <t>user-444@example.com</t>
@@ -19869,11 +19683,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D450" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E450" s="0">
         <v>24.4</v>
       </c>
@@ -19922,6 +19731,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E451" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F451" s="0" t="inlineStr">
         <is>
           <t>user-449@example.com</t>
@@ -20005,6 +19817,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D453" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E453" s="0">
         <v>24.4</v>
       </c>
@@ -20048,6 +19865,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E454" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F454" s="0" t="inlineStr">
         <is>
           <t>user-452@example.com</t>
@@ -20088,9 +19908,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E455" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F455" s="0" t="inlineStr">
         <is>
           <t>user-453@example.com</t>
@@ -20131,9 +19948,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E456" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F456" s="0" t="inlineStr">
         <is>
           <t>user-454@example.com</t>
@@ -20174,6 +19988,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D457" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F457" s="0" t="inlineStr">
         <is>
           <t>user-455@example.com</t>
@@ -20214,6 +20033,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D458" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E458" s="0">
         <v>24.4</v>
       </c>
@@ -20257,11 +20081,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D459" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E459" s="0">
         <v>24.4</v>
       </c>
@@ -20305,11 +20124,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D460" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F460" s="0" t="inlineStr">
         <is>
           <t>user-458@example.com</t>
@@ -20350,11 +20164,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D461" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E461" s="0">
         <v>24.4</v>
       </c>
@@ -20441,6 +20250,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D463" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E463" s="0">
         <v>24.4</v>
       </c>
@@ -20524,6 +20338,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E465" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F465" s="0" t="inlineStr">
         <is>
           <t>user-463@example.com</t>
@@ -20604,6 +20421,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E467" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F467" s="0" t="inlineStr">
         <is>
           <t>user-465@example.com</t>
@@ -20644,6 +20464,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D468" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E468" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F468" s="0" t="inlineStr">
         <is>
           <t>user-466@example.com</t>
@@ -20684,9 +20512,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E469" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F469" s="0" t="inlineStr">
         <is>
           <t>user-467@example.com</t>
@@ -20727,11 +20552,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D470" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F470" s="0" t="inlineStr">
         <is>
           <t>user-468@example.com</t>
@@ -20772,6 +20592,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E471" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F471" s="0" t="inlineStr">
         <is>
           <t>user-469@example.com</t>
@@ -20812,10 +20635,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D472" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E472" s="0">
+        <v>24.4</v>
       </c>
       <c r="F472" s="0" t="inlineStr">
         <is>
@@ -20857,9 +20678,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E473" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F473" s="0" t="inlineStr">
         <is>
           <t>user-471@example.com</t>
@@ -20940,14 +20758,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D475" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E475" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F475" s="0" t="inlineStr">
         <is>
           <t>user-473@example.com</t>
@@ -21036,6 +20846,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D477" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E477" s="0">
         <v>24.4</v>
       </c>
@@ -21079,10 +20894,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D478" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E478" s="0">
+        <v>24.4</v>
       </c>
       <c r="F478" s="0" t="inlineStr">
         <is>
@@ -21167,6 +20980,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D480" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E480" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F480" s="0" t="inlineStr">
         <is>
           <t>user-478@example.com</t>
@@ -21252,6 +21073,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D482" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F482" s="0" t="inlineStr">
         <is>
           <t>user-480@example.com</t>
@@ -21292,6 +21118,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D483" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E483" s="0">
         <v>24.4</v>
       </c>
@@ -21340,6 +21171,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E484" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F484" s="0" t="inlineStr">
         <is>
           <t>user-482@example.com</t>
@@ -21380,11 +21214,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D485" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F485" s="0" t="inlineStr">
         <is>
           <t>user-483@example.com</t>
@@ -21425,6 +21254,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D486" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F486" s="0" t="inlineStr">
         <is>
           <t>user-484@example.com</t>
@@ -21465,9 +21299,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E487" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F487" s="0" t="inlineStr">
         <is>
           <t>user-485@example.com</t>
@@ -21508,11 +21339,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D488" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E488" s="0">
         <v>24.4</v>
       </c>
@@ -21556,14 +21382,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D489" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E489" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F489" s="0" t="inlineStr">
         <is>
           <t>user-487@example.com</t>
@@ -21609,6 +21427,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E490" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F490" s="0" t="inlineStr">
         <is>
           <t>user-488@example.com</t>
@@ -21689,14 +21510,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D492" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E492" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F492" s="0" t="inlineStr">
         <is>
           <t>user-490@example.com</t>
@@ -21780,11 +21593,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D494" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F494" s="0" t="inlineStr">
         <is>
           <t>user-492@example.com</t>
@@ -21830,9 +21638,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E495" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F495" s="0" t="inlineStr">
         <is>
           <t>user-493@example.com</t>
@@ -21873,6 +21678,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D496" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E496" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F496" s="0" t="inlineStr">
         <is>
           <t>user-494@example.com</t>
@@ -21913,6 +21726,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D497" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F497" s="0" t="inlineStr">
         <is>
           <t>user-495@example.com</t>
@@ -21953,9 +21771,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E498" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F498" s="0" t="inlineStr">
         <is>
           <t>user-496@example.com</t>
@@ -22041,9 +21856,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E500" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F500" s="0" t="inlineStr">
         <is>
           <t>user-498@example.com</t>
@@ -22084,6 +21896,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D501" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E501" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F501" s="0" t="inlineStr">
         <is>
           <t>user-499@example.com</t>
@@ -22129,9 +21949,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E502" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F502" s="0" t="inlineStr">
         <is>
           <t>user-500@example.com</t>
@@ -22212,11 +22029,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D504" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F504" s="0" t="inlineStr">
         <is>
           <t>user-502@example.com</t>
@@ -22257,6 +22069,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D505" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E505" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F505" s="0" t="inlineStr">
         <is>
           <t>user-503@example.com</t>
@@ -22297,14 +22117,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D506" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E506" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F506" s="0" t="inlineStr">
         <is>
           <t>user-504@example.com</t>
@@ -22393,6 +22205,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D508" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E508" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F508" s="0" t="inlineStr">
         <is>
           <t>user-506@example.com</t>
@@ -22433,6 +22253,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D509" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E509" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F509" s="0" t="inlineStr">
         <is>
           <t>user-507@example.com</t>
@@ -22473,8 +22301,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E510" s="0">
-        <v>24.4</v>
+      <c r="D510" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F510" s="0" t="inlineStr">
         <is>
@@ -22516,6 +22346,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D511" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E511" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F511" s="0" t="inlineStr">
         <is>
           <t>user-509@example.com</t>
@@ -22556,11 +22394,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D512" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E512" s="0">
         <v>24.4</v>
       </c>
@@ -22684,8 +22517,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E515" s="0">
-        <v>24.4</v>
+      <c r="D515" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F515" s="0" t="inlineStr">
         <is>
@@ -22732,9 +22567,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E516" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F516" s="0" t="inlineStr">
         <is>
           <t>user-514@example.com</t>
@@ -22780,9 +22612,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E517" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F517" s="0" t="inlineStr">
         <is>
           <t>user-515@example.com</t>
@@ -22823,10 +22652,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D518" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E518" s="0">
+        <v>24.4</v>
       </c>
       <c r="F518" s="0" t="inlineStr">
         <is>
@@ -22868,6 +22695,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D519" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E519" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F519" s="0" t="inlineStr">
         <is>
           <t>user-517@example.com</t>
@@ -22908,6 +22743,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D520" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E520" s="0">
         <v>24.4</v>
       </c>
@@ -23004,9 +22844,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E522" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F522" s="0" t="inlineStr">
         <is>
           <t>user-520@example.com</t>
@@ -23047,8 +22884,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E523" s="0">
-        <v>24.4</v>
+      <c r="D523" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F523" s="0" t="inlineStr">
         <is>
@@ -23090,6 +22929,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D524" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E524" s="0">
         <v>24.4</v>
       </c>
@@ -23133,14 +22977,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D525" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E525" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F525" s="0" t="inlineStr">
         <is>
           <t>user-523@example.com</t>
@@ -23181,6 +23017,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D526" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E526" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F526" s="0" t="inlineStr">
         <is>
           <t>user-524@example.com</t>
@@ -23226,6 +23070,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E527" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F527" s="0" t="inlineStr">
         <is>
           <t>user-525@example.com</t>
@@ -23271,6 +23118,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E528" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F528" s="0" t="inlineStr">
         <is>
           <t>user-526@example.com</t>
@@ -23359,6 +23209,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D530" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F530" s="0" t="inlineStr">
         <is>
           <t>user-528@example.com</t>
@@ -23399,6 +23254,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E531" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F531" s="0" t="inlineStr">
         <is>
           <t>user-529@example.com</t>
@@ -23439,6 +23297,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D532" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E532" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F532" s="0" t="inlineStr">
         <is>
           <t>user-530@example.com</t>
@@ -23484,9 +23350,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E533" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F533" s="0" t="inlineStr">
         <is>
           <t>user-531@example.com</t>
@@ -23527,8 +23390,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E534" s="0">
-        <v>24.4</v>
+      <c r="D534" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F534" s="0" t="inlineStr">
         <is>
@@ -23610,10 +23475,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D536" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E536" s="0">
+        <v>24.4</v>
       </c>
       <c r="F536" s="0" t="inlineStr">
         <is>
@@ -23698,8 +23561,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E538" s="0">
-        <v>24.4</v>
+      <c r="D538" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F538" s="0" t="inlineStr">
         <is>
@@ -23741,6 +23606,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D539" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E539" s="0">
         <v>24.4</v>
       </c>
@@ -23784,6 +23654,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E540" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F540" s="0" t="inlineStr">
         <is>
           <t>user-538@example.com</t>
@@ -23829,6 +23702,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E541" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F541" s="0" t="inlineStr">
         <is>
           <t>user-539@example.com</t>
@@ -23869,6 +23745,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D542" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E542" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F542" s="0" t="inlineStr">
         <is>
           <t>user-540@example.com</t>
@@ -23909,6 +23793,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E543" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F543" s="0" t="inlineStr">
         <is>
           <t>user-541@example.com</t>
@@ -23949,6 +23836,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D544" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E544" s="0">
         <v>24.4</v>
       </c>
@@ -24037,9 +23929,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E546" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F546" s="0" t="inlineStr">
         <is>
           <t>user-544@example.com</t>
@@ -24176,9 +24065,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E549" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F549" s="0" t="inlineStr">
         <is>
           <t>user-547@example.com</t>
@@ -24219,14 +24105,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D550" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E550" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F550" s="0" t="inlineStr">
         <is>
           <t>user-548@example.com</t>
@@ -24307,6 +24185,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D552" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E552" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F552" s="0" t="inlineStr">
         <is>
           <t>user-550@example.com</t>
@@ -24352,9 +24238,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E553" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F553" s="0" t="inlineStr">
         <is>
           <t>user-551@example.com</t>
@@ -24395,11 +24278,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D554" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E554" s="0">
         <v>24.4</v>
       </c>
@@ -24443,6 +24321,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D555" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E555" s="0">
         <v>24.4</v>
       </c>
@@ -24486,9 +24369,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E556" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F556" s="0" t="inlineStr">
         <is>
           <t>user-554@example.com</t>
@@ -24529,6 +24409,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D557" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E557" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F557" s="0" t="inlineStr">
         <is>
           <t>user-555@example.com</t>
@@ -24574,6 +24462,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E558" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F558" s="0" t="inlineStr">
         <is>
           <t>user-556@example.com</t>
@@ -24614,11 +24505,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D559" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E559" s="0">
         <v>24.4</v>
       </c>
@@ -24667,9 +24553,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E560" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F560" s="0" t="inlineStr">
         <is>
           <t>user-558@example.com</t>
@@ -24715,9 +24598,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E561" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F561" s="0" t="inlineStr">
         <is>
           <t>user-559@example.com</t>
@@ -24758,10 +24638,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D562" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E562" s="0">
+        <v>24.4</v>
       </c>
       <c r="F562" s="0" t="inlineStr">
         <is>
@@ -24803,9 +24681,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E563" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F563" s="0" t="inlineStr">
         <is>
           <t>user-561@example.com</t>
@@ -24846,10 +24721,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D564" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E564" s="0">
+        <v>24.4</v>
       </c>
       <c r="F564" s="0" t="inlineStr">
         <is>
@@ -24891,8 +24764,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E565" s="0">
-        <v>24.4</v>
+      <c r="D565" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F565" s="0" t="inlineStr">
         <is>
@@ -24934,11 +24809,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D566" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F566" s="0" t="inlineStr">
         <is>
           <t>user-564@example.com</t>
@@ -24979,11 +24849,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D567" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F567" s="0" t="inlineStr">
         <is>
           <t>user-565@example.com</t>
@@ -25024,6 +24889,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D568" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E568" s="0">
         <v>24.4</v>
       </c>
@@ -25147,10 +25017,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D571" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E571" s="0">
+        <v>24.4</v>
       </c>
       <c r="F571" s="0" t="inlineStr">
         <is>
@@ -25192,9 +25060,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E572" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F572" s="0" t="inlineStr">
         <is>
           <t>user-570@example.com</t>
@@ -25280,6 +25145,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D574" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E574" s="0">
         <v>24.4</v>
       </c>
@@ -25323,8 +25193,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E575" s="0">
-        <v>24.4</v>
+      <c r="D575" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F575" s="0" t="inlineStr">
         <is>
@@ -25371,9 +25243,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E576" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F576" s="0" t="inlineStr">
         <is>
           <t>user-574@example.com</t>
@@ -25414,6 +25283,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D577" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E577" s="0">
         <v>24.4</v>
       </c>
@@ -25462,9 +25336,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E578" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F578" s="0" t="inlineStr">
         <is>
           <t>user-576@example.com</t>
@@ -25505,8 +25376,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E579" s="0">
-        <v>24.4</v>
+      <c r="D579" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F579" s="0" t="inlineStr">
         <is>
@@ -25593,10 +25466,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D581" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E581" s="0">
+        <v>24.4</v>
       </c>
       <c r="F581" s="0" t="inlineStr">
         <is>
@@ -25643,9 +25514,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E582" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F582" s="0" t="inlineStr">
         <is>
           <t>user-580@example.com</t>
@@ -25686,6 +25554,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D583" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F583" s="0" t="inlineStr">
         <is>
           <t>user-581@example.com</t>
@@ -25769,6 +25642,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D585" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E585" s="0">
         <v>24.4</v>
       </c>
@@ -25812,11 +25690,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D586" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E586" s="0">
         <v>24.4</v>
       </c>
@@ -25860,11 +25733,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D587" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E587" s="0">
         <v>24.4</v>
       </c>
@@ -25908,14 +25776,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D588" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E588" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F588" s="0" t="inlineStr">
         <is>
           <t>user-586@example.com</t>
@@ -25956,9 +25816,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E589" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F589" s="0" t="inlineStr">
         <is>
           <t>user-587@example.com</t>
@@ -25999,9 +25856,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E590" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F590" s="0" t="inlineStr">
         <is>
           <t>user-588@example.com</t>
@@ -26042,9 +25896,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E591" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F591" s="0" t="inlineStr">
         <is>
           <t>user-589@example.com</t>
@@ -26090,6 +25941,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E592" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F592" s="0" t="inlineStr">
         <is>
           <t>user-590@example.com</t>
@@ -26130,6 +25984,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D593" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E593" s="0">
         <v>24.4</v>
       </c>
@@ -26173,11 +26032,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D594" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E594" s="0">
         <v>24.4</v>
       </c>
@@ -26221,8 +26075,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E595" s="0">
-        <v>24.4</v>
+      <c r="D595" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F595" s="0" t="inlineStr">
         <is>
@@ -26264,9 +26120,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E596" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F596" s="0" t="inlineStr">
         <is>
           <t>user-594@example.com</t>
@@ -26307,11 +26160,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D597" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E597" s="0">
         <v>24.4</v>
       </c>
@@ -26499,9 +26347,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E601" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F601" s="0" t="inlineStr">
         <is>
           <t>user-599@example.com</t>
@@ -26670,11 +26515,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D605" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E605" s="0">
         <v>24.4</v>
       </c>
@@ -26768,6 +26608,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E607" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F607" s="0" t="inlineStr">
         <is>
           <t>user-605@example.com</t>
@@ -26808,11 +26651,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D608" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F608" s="0" t="inlineStr">
         <is>
           <t>user-606@example.com</t>
@@ -26853,14 +26691,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D609" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E609" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F609" s="0" t="inlineStr">
         <is>
           <t>user-607@example.com</t>
@@ -26901,10 +26731,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D610" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E610" s="0">
+        <v>24.4</v>
       </c>
       <c r="F610" s="0" t="inlineStr">
         <is>
@@ -26946,8 +26774,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E611" s="0">
-        <v>24.4</v>
+      <c r="D611" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F611" s="0" t="inlineStr">
         <is>
@@ -26989,11 +26819,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D612" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F612" s="0" t="inlineStr">
         <is>
           <t>user-610@example.com</t>
@@ -27082,6 +26907,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E614" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F614" s="0" t="inlineStr">
         <is>
           <t>user-612@example.com</t>
@@ -27122,9 +26950,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E615" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F615" s="0" t="inlineStr">
         <is>
           <t>user-613@example.com</t>
@@ -27165,6 +26990,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D616" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F616" s="0" t="inlineStr">
         <is>
           <t>user-614@example.com</t>
@@ -27210,6 +27040,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E617" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F617" s="0" t="inlineStr">
         <is>
           <t>user-615@example.com</t>
@@ -27250,14 +27083,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D618" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E618" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F618" s="0" t="inlineStr">
         <is>
           <t>user-616@example.com</t>
@@ -27298,14 +27123,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D619" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E619" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F619" s="0" t="inlineStr">
         <is>
           <t>user-617@example.com</t>
@@ -27346,11 +27163,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D620" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F620" s="0" t="inlineStr">
         <is>
           <t>user-618@example.com</t>
@@ -27391,6 +27203,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D621" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E621" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F621" s="0" t="inlineStr">
         <is>
           <t>user-619@example.com</t>
@@ -27431,9 +27251,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E622" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F622" s="0" t="inlineStr">
         <is>
           <t>user-620@example.com</t>
@@ -27474,14 +27291,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D623" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E623" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F623" s="0" t="inlineStr">
         <is>
           <t>user-621@example.com</t>
@@ -27522,9 +27331,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E624" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F624" s="0" t="inlineStr">
         <is>
           <t>user-622@example.com</t>
@@ -27608,6 +27414,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E626" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F626" s="0" t="inlineStr">
         <is>
           <t>user-624@example.com</t>
@@ -27653,9 +27462,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E627" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F627" s="0" t="inlineStr">
         <is>
           <t>user-625@example.com</t>
@@ -27701,6 +27507,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E628" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F628" s="0" t="inlineStr">
         <is>
           <t>user-626@example.com</t>
@@ -27746,9 +27555,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E629" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F629" s="0" t="inlineStr">
         <is>
           <t>user-627@example.com</t>
@@ -27920,9 +27726,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E633" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F633" s="0" t="inlineStr">
         <is>
           <t>user-631@example.com</t>
@@ -27963,6 +27766,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D634" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E634" s="0">
         <v>24.4</v>
       </c>
@@ -28006,6 +27814,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E635" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F635" s="0" t="inlineStr">
         <is>
           <t>user-633@example.com</t>
@@ -28046,6 +27857,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D636" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E636" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F636" s="0" t="inlineStr">
         <is>
           <t>user-634@example.com</t>
@@ -28086,6 +27905,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E637" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F637" s="0" t="inlineStr">
         <is>
           <t>user-635@example.com</t>
@@ -28126,6 +27948,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D638" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E638" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F638" s="0" t="inlineStr">
         <is>
           <t>user-636@example.com</t>
@@ -28171,6 +28001,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E639" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F639" s="0" t="inlineStr">
         <is>
           <t>user-637@example.com</t>
@@ -28211,9 +28044,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E640" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F640" s="0" t="inlineStr">
         <is>
           <t>user-638@example.com</t>
@@ -28254,8 +28084,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E641" s="0">
-        <v>24.4</v>
+      <c r="D641" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F641" s="0" t="inlineStr">
         <is>
@@ -28297,6 +28129,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D642" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F642" s="0" t="inlineStr">
         <is>
           <t>user-640@example.com</t>
@@ -28382,6 +28219,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D644" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F644" s="0" t="inlineStr">
         <is>
           <t>user-642@example.com</t>
@@ -28422,6 +28264,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E645" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F645" s="0" t="inlineStr">
         <is>
           <t>user-643@example.com</t>
@@ -28552,6 +28397,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E648" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F648" s="0" t="inlineStr">
         <is>
           <t>user-646@example.com</t>
@@ -28592,9 +28440,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E649" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F649" s="0" t="inlineStr">
         <is>
           <t>user-647@example.com</t>
@@ -28635,11 +28480,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D650" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F650" s="0" t="inlineStr">
         <is>
           <t>user-648@example.com</t>
@@ -28680,11 +28520,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D651" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E651" s="0">
         <v>24.4</v>
       </c>
@@ -28728,6 +28563,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D652" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E652" s="0">
         <v>24.4</v>
       </c>
@@ -28776,6 +28616,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E653" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F653" s="0" t="inlineStr">
         <is>
           <t>user-651@example.com</t>
@@ -28816,14 +28659,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D654" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E654" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F654" s="0" t="inlineStr">
         <is>
           <t>user-652@example.com</t>
@@ -28869,6 +28704,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E655" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F655" s="0" t="inlineStr">
         <is>
           <t>user-653@example.com</t>
@@ -28909,8 +28747,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E656" s="0">
-        <v>24.4</v>
+      <c r="D656" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F656" s="0" t="inlineStr">
         <is>
@@ -29085,11 +28925,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D660" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F660" s="0" t="inlineStr">
         <is>
           <t>user-658@example.com</t>
@@ -29130,6 +28965,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E661" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F661" s="0" t="inlineStr">
         <is>
           <t>user-659@example.com</t>
@@ -29170,6 +29008,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D662" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E662" s="0">
         <v>24.4</v>
       </c>
@@ -29213,10 +29056,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D663" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E663" s="0">
+        <v>24.4</v>
       </c>
       <c r="F663" s="0" t="inlineStr">
         <is>
@@ -29258,9 +29099,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E664" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F664" s="0" t="inlineStr">
         <is>
           <t>user-662@example.com</t>
@@ -29301,11 +29139,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D665" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F665" s="0" t="inlineStr">
         <is>
           <t>user-663@example.com</t>
@@ -29346,6 +29179,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D666" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E666" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F666" s="0" t="inlineStr">
         <is>
           <t>user-664@example.com</t>
@@ -29391,9 +29232,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E667" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F667" s="0" t="inlineStr">
         <is>
           <t>user-665@example.com</t>
@@ -29479,6 +29317,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D669" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F669" s="0" t="inlineStr">
         <is>
           <t>user-667@example.com</t>
@@ -29519,11 +29362,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D670" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F670" s="0" t="inlineStr">
         <is>
           <t>user-668@example.com</t>
@@ -29564,11 +29402,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D671" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F671" s="0" t="inlineStr">
         <is>
           <t>user-669@example.com</t>
@@ -29609,11 +29442,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D672" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E672" s="0">
         <v>24.4</v>
       </c>
@@ -29657,6 +29485,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D673" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F673" s="0" t="inlineStr">
         <is>
           <t>user-671@example.com</t>
@@ -29737,6 +29570,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D675" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F675" s="0" t="inlineStr">
         <is>
           <t>user-673@example.com</t>
@@ -29782,9 +29620,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E676" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F676" s="0" t="inlineStr">
         <is>
           <t>user-674@example.com</t>
@@ -29825,9 +29660,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E677" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F677" s="0" t="inlineStr">
         <is>
           <t>user-675@example.com</t>
@@ -29913,10 +29745,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D679" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E679" s="0">
+        <v>24.4</v>
       </c>
       <c r="F679" s="0" t="inlineStr">
         <is>
@@ -29958,6 +29788,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D680" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E680" s="0">
         <v>24.4</v>
       </c>
@@ -30001,8 +29836,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E681" s="0">
-        <v>24.4</v>
+      <c r="D681" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F681" s="0" t="inlineStr">
         <is>
@@ -30092,11 +29929,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D683" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E683" s="0">
         <v>24.4</v>
       </c>
@@ -30140,6 +29972,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E684" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F684" s="0" t="inlineStr">
         <is>
           <t>user-682@example.com</t>
@@ -30362,6 +30197,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E689" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F689" s="0" t="inlineStr">
         <is>
           <t>user-687@example.com</t>
@@ -30402,11 +30240,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D690" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E690" s="0">
         <v>24.4</v>
       </c>
@@ -30450,6 +30283,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D691" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F691" s="0" t="inlineStr">
         <is>
           <t>user-689@example.com</t>
@@ -30490,9 +30328,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E692" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F692" s="0" t="inlineStr">
         <is>
           <t>user-690@example.com</t>
@@ -30581,8 +30416,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E694" s="0">
-        <v>24.4</v>
+      <c r="D694" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F694" s="0" t="inlineStr">
         <is>
@@ -30832,14 +30669,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D700" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E700" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F700" s="0" t="inlineStr">
         <is>
           <t>user-698@example.com</t>
@@ -30885,9 +30714,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E701" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F701" s="0" t="inlineStr">
         <is>
           <t>user-699@example.com</t>
@@ -30928,14 +30754,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D702" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E702" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F702" s="0" t="inlineStr">
         <is>
           <t>user-700@example.com</t>
@@ -30976,10 +30794,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D703" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E703" s="0">
+        <v>24.4</v>
       </c>
       <c r="F703" s="0" t="inlineStr">
         <is>
@@ -31026,9 +30842,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E704" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F704" s="0" t="inlineStr">
         <is>
           <t>user-702@example.com</t>
@@ -31074,6 +30887,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E705" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F705" s="0" t="inlineStr">
         <is>
           <t>user-703@example.com</t>
@@ -31114,6 +30930,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D706" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E706" s="0">
         <v>24.4</v>
       </c>
@@ -31240,14 +31061,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D709" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E709" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F709" s="0" t="inlineStr">
         <is>
           <t>user-707@example.com</t>
@@ -31288,14 +31101,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D710" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E710" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F710" s="0" t="inlineStr">
         <is>
           <t>user-708@example.com</t>
@@ -31336,11 +31141,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D711" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E711" s="0">
         <v>24.4</v>
       </c>
@@ -31384,6 +31184,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E712" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F712" s="0" t="inlineStr">
         <is>
           <t>user-710@example.com</t>
@@ -31472,6 +31275,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D714" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E714" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F714" s="0" t="inlineStr">
         <is>
           <t>user-712@example.com</t>
@@ -31597,6 +31408,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E717" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F717" s="0" t="inlineStr">
         <is>
           <t>user-715@example.com</t>
@@ -31637,9 +31451,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E718" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F718" s="0" t="inlineStr">
         <is>
           <t>user-716@example.com</t>
@@ -31766,10 +31577,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D721" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E721" s="0">
+        <v>24.4</v>
       </c>
       <c r="F721" s="0" t="inlineStr">
         <is>
@@ -31856,6 +31665,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E723" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F723" s="0" t="inlineStr">
         <is>
           <t>user-721@example.com</t>
@@ -31896,11 +31708,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D724" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F724" s="0" t="inlineStr">
         <is>
           <t>user-722@example.com</t>
@@ -31941,6 +31748,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D725" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E725" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F725" s="0" t="inlineStr">
         <is>
           <t>user-723@example.com</t>
@@ -31981,11 +31796,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D726" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F726" s="0" t="inlineStr">
         <is>
           <t>user-724@example.com</t>
@@ -32066,9 +31876,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E728" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F728" s="0" t="inlineStr">
         <is>
           <t>user-726@example.com</t>
@@ -32109,14 +31916,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D729" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E729" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F729" s="0" t="inlineStr">
         <is>
           <t>user-727@example.com</t>
@@ -32237,8 +32036,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E732" s="0">
-        <v>24.4</v>
+      <c r="D732" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F732" s="0" t="inlineStr">
         <is>
@@ -32285,9 +32086,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E733" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F733" s="0" t="inlineStr">
         <is>
           <t>user-731@example.com</t>
@@ -32328,8 +32126,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E734" s="0">
-        <v>24.4</v>
+      <c r="D734" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F734" s="0" t="inlineStr">
         <is>
@@ -32371,6 +32171,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E735" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F735" s="0" t="inlineStr">
         <is>
           <t>user-733@example.com</t>
@@ -32416,9 +32219,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E736" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F736" s="0" t="inlineStr">
         <is>
           <t>user-734@example.com</t>
@@ -32459,10 +32259,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D737" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E737" s="0">
+        <v>24.4</v>
       </c>
       <c r="F737" s="0" t="inlineStr">
         <is>
@@ -32504,6 +32302,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D738" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E738" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F738" s="0" t="inlineStr">
         <is>
           <t>user-736@example.com</t>
@@ -32544,6 +32350,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D739" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E739" s="0">
         <v>24.4</v>
       </c>
@@ -32632,10 +32443,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D741" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E741" s="0">
+        <v>24.4</v>
       </c>
       <c r="F741" s="0" t="inlineStr">
         <is>
@@ -32682,9 +32491,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E742" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F742" s="0" t="inlineStr">
         <is>
           <t>user-740@example.com</t>
@@ -32725,11 +32531,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D743" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F743" s="0" t="inlineStr">
         <is>
           <t>user-741@example.com</t>
@@ -32770,6 +32571,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E744" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F744" s="0" t="inlineStr">
         <is>
           <t>user-742@example.com</t>
@@ -32810,6 +32614,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D745" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E745" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F745" s="0" t="inlineStr">
         <is>
           <t>user-743@example.com</t>
@@ -32850,10 +32662,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D746" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E746" s="0">
+        <v>24.4</v>
       </c>
       <c r="F746" s="0" t="inlineStr">
         <is>
@@ -32981,8 +32791,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E749" s="0">
-        <v>24.4</v>
+      <c r="D749" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F749" s="0" t="inlineStr">
         <is>
@@ -33024,6 +32836,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E750" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F750" s="0" t="inlineStr">
         <is>
           <t>user-748@example.com</t>
@@ -33104,8 +32919,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E752" s="0">
-        <v>24.4</v>
+      <c r="D752" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F752" s="0" t="inlineStr">
         <is>
@@ -33147,6 +32964,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D753" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F753" s="0" t="inlineStr">
         <is>
           <t>user-751@example.com</t>
@@ -33187,10 +33009,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D754" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E754" s="0">
+        <v>24.4</v>
       </c>
       <c r="F754" s="0" t="inlineStr">
         <is>
@@ -33232,10 +33052,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D755" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E755" s="0">
+        <v>24.4</v>
       </c>
       <c r="F755" s="0" t="inlineStr">
         <is>
@@ -33282,9 +33100,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E756" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F756" s="0" t="inlineStr">
         <is>
           <t>user-754@example.com</t>
@@ -33365,10 +33180,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D758" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E758" s="0">
+        <v>24.4</v>
       </c>
       <c r="F758" s="0" t="inlineStr">
         <is>
@@ -33410,10 +33223,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D759" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E759" s="0">
+        <v>24.4</v>
       </c>
       <c r="F759" s="0" t="inlineStr">
         <is>
@@ -33455,6 +33266,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E760" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F760" s="0" t="inlineStr">
         <is>
           <t>user-758@example.com</t>
@@ -33495,6 +33309,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D761" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F761" s="0" t="inlineStr">
         <is>
           <t>user-759@example.com</t>
@@ -33623,6 +33442,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D764" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F764" s="0" t="inlineStr">
         <is>
           <t>user-762@example.com</t>
@@ -33663,9 +33487,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E765" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F765" s="0" t="inlineStr">
         <is>
           <t>user-763@example.com</t>
@@ -33746,14 +33567,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D767" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E767" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F767" s="0" t="inlineStr">
         <is>
           <t>user-765@example.com</t>
@@ -33794,11 +33607,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D768" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F768" s="0" t="inlineStr">
         <is>
           <t>user-766@example.com</t>
@@ -33839,14 +33647,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D769" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E769" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F769" s="0" t="inlineStr">
         <is>
           <t>user-767@example.com</t>
@@ -33932,6 +33732,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D771" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F771" s="0" t="inlineStr">
         <is>
           <t>user-769@example.com</t>
@@ -33972,14 +33777,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D772" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E772" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F772" s="0" t="inlineStr">
         <is>
           <t>user-770@example.com</t>
@@ -34020,6 +33817,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D773" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E773" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F773" s="0" t="inlineStr">
         <is>
           <t>user-771@example.com</t>
@@ -34060,6 +33865,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D774" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E774" s="0">
         <v>24.4</v>
       </c>
@@ -34103,14 +33913,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D775" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E775" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F775" s="0" t="inlineStr">
         <is>
           <t>user-773@example.com</t>
@@ -34194,8 +33996,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E777" s="0">
-        <v>24.4</v>
+      <c r="D777" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F777" s="0" t="inlineStr">
         <is>
@@ -34237,9 +34041,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E778" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F778" s="0" t="inlineStr">
         <is>
           <t>user-776@example.com</t>
@@ -34280,6 +34081,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D779" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E779" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F779" s="0" t="inlineStr">
         <is>
           <t>user-777@example.com</t>
@@ -34365,14 +34174,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D781" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E781" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F781" s="0" t="inlineStr">
         <is>
           <t>user-779@example.com</t>
@@ -34413,6 +34214,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D782" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E782" s="0">
         <v>24.4</v>
       </c>
@@ -34456,11 +34262,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D783" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F783" s="0" t="inlineStr">
         <is>
           <t>user-781@example.com</t>
@@ -34506,9 +34307,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E784" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F784" s="0" t="inlineStr">
         <is>
           <t>user-782@example.com</t>
@@ -34594,6 +34392,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D786" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E786" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F786" s="0" t="inlineStr">
         <is>
           <t>user-784@example.com</t>
@@ -34687,6 +34493,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E788" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F788" s="0" t="inlineStr">
         <is>
           <t>user-786@example.com</t>
@@ -34727,11 +34536,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D789" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F789" s="0" t="inlineStr">
         <is>
           <t>user-787@example.com</t>
@@ -34772,8 +34576,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E790" s="0">
-        <v>24.4</v>
+      <c r="D790" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F790" s="0" t="inlineStr">
         <is>
@@ -34863,9 +34669,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E792" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F792" s="0" t="inlineStr">
         <is>
           <t>user-790@example.com</t>
@@ -34906,6 +34709,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D793" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E793" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F793" s="0" t="inlineStr">
         <is>
           <t>user-791@example.com</t>
@@ -35039,6 +34850,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E796" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F796" s="0" t="inlineStr">
         <is>
           <t>user-794@example.com</t>
@@ -35079,9 +34893,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E797" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F797" s="0" t="inlineStr">
         <is>
           <t>user-795@example.com</t>
@@ -35122,8 +34933,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E798" s="0">
-        <v>24.4</v>
+      <c r="D798" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F798" s="0" t="inlineStr">
         <is>
@@ -35290,6 +35103,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D802" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E802" s="0">
         <v>24.4</v>
       </c>
@@ -35333,10 +35151,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D803" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E803" s="0">
+        <v>24.4</v>
       </c>
       <c r="F803" s="0" t="inlineStr">
         <is>
@@ -35378,8 +35194,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E804" s="0">
-        <v>24.4</v>
+      <c r="D804" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F804" s="0" t="inlineStr">
         <is>
@@ -35421,14 +35239,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D805" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E805" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F805" s="0" t="inlineStr">
         <is>
           <t>user-803@example.com</t>
@@ -35469,8 +35279,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E806" s="0">
-        <v>24.4</v>
+      <c r="D806" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F806" s="0" t="inlineStr">
         <is>
@@ -35512,11 +35324,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D807" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F807" s="0" t="inlineStr">
         <is>
           <t>user-805@example.com</t>
@@ -35597,14 +35404,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D809" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E809" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F809" s="0" t="inlineStr">
         <is>
           <t>user-807@example.com</t>
@@ -35645,9 +35444,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E810" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F810" s="0" t="inlineStr">
         <is>
           <t>user-808@example.com</t>
@@ -35688,10 +35484,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D811" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E811" s="0">
+        <v>24.4</v>
       </c>
       <c r="F811" s="0" t="inlineStr">
         <is>
@@ -35733,11 +35527,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D812" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F812" s="0" t="inlineStr">
         <is>
           <t>user-810@example.com</t>
@@ -35778,6 +35567,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D813" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E813" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F813" s="0" t="inlineStr">
         <is>
           <t>user-811@example.com</t>
@@ -35823,6 +35620,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E814" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F814" s="0" t="inlineStr">
         <is>
           <t>user-812@example.com</t>
@@ -35863,10 +35663,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D815" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E815" s="0">
+        <v>24.4</v>
       </c>
       <c r="F815" s="0" t="inlineStr">
         <is>
@@ -35908,6 +35706,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E816" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F816" s="0" t="inlineStr">
         <is>
           <t>user-814@example.com</t>
@@ -35991,9 +35792,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E818" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F818" s="0" t="inlineStr">
         <is>
           <t>user-816@example.com</t>
@@ -36034,10 +35832,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D819" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E819" s="0">
+        <v>24.4</v>
       </c>
       <c r="F819" s="0" t="inlineStr">
         <is>
@@ -36079,11 +35875,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D820" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F820" s="0" t="inlineStr">
         <is>
           <t>user-818@example.com</t>
@@ -36124,8 +35915,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E821" s="0">
-        <v>24.4</v>
+      <c r="D821" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F821" s="0" t="inlineStr">
         <is>
@@ -36167,11 +35960,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D822" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F822" s="0" t="inlineStr">
         <is>
           <t>user-820@example.com</t>
@@ -36212,6 +36000,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D823" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E823" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F823" s="0" t="inlineStr">
         <is>
           <t>user-821@example.com</t>
@@ -36252,14 +36048,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D824" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E824" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F824" s="0" t="inlineStr">
         <is>
           <t>user-822@example.com</t>
@@ -36343,6 +36131,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D826" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E826" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F826" s="0" t="inlineStr">
         <is>
           <t>user-824@example.com</t>
@@ -36383,6 +36179,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D827" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E827" s="0">
         <v>24.4</v>
       </c>
@@ -36517,6 +36318,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D830" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F830" s="0" t="inlineStr">
         <is>
           <t>user-828@example.com</t>
@@ -36557,6 +36363,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D831" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E831" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F831" s="0" t="inlineStr">
         <is>
           <t>user-829@example.com</t>
@@ -36597,9 +36411,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E832" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F832" s="0" t="inlineStr">
         <is>
           <t>user-830@example.com</t>
@@ -36640,11 +36451,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D833" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F833" s="0" t="inlineStr">
         <is>
           <t>user-831@example.com</t>
@@ -36730,11 +36536,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D835" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E835" s="0">
         <v>24.4</v>
       </c>
@@ -36818,11 +36619,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D837" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E837" s="0">
         <v>24.4</v>
       </c>
@@ -36866,14 +36662,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D838" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E838" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F838" s="0" t="inlineStr">
         <is>
           <t>user-836@example.com</t>
@@ -36914,14 +36702,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D839" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E839" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F839" s="0" t="inlineStr">
         <is>
           <t>user-837@example.com</t>
@@ -36962,6 +36742,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D840" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E840" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F840" s="0" t="inlineStr">
         <is>
           <t>user-838@example.com</t>
@@ -37050,8 +36838,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E842" s="0">
-        <v>24.4</v>
+      <c r="D842" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F842" s="0" t="inlineStr">
         <is>
@@ -37141,10 +36931,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D844" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E844" s="0">
+        <v>24.4</v>
       </c>
       <c r="F844" s="0" t="inlineStr">
         <is>
@@ -37186,6 +36974,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D845" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F845" s="0" t="inlineStr">
         <is>
           <t>user-843@example.com</t>
@@ -37226,6 +37019,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E846" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F846" s="0" t="inlineStr">
         <is>
           <t>user-844@example.com</t>
@@ -37266,6 +37062,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D847" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E847" s="0">
         <v>24.4</v>
       </c>
@@ -37309,9 +37110,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E848" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F848" s="0" t="inlineStr">
         <is>
           <t>user-846@example.com</t>
@@ -37352,9 +37150,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E849" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F849" s="0" t="inlineStr">
         <is>
           <t>user-847@example.com</t>
@@ -37395,11 +37190,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D850" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E850" s="0">
         <v>24.4</v>
       </c>
@@ -37443,14 +37233,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D851" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E851" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F851" s="0" t="inlineStr">
         <is>
           <t>user-849@example.com</t>
@@ -37491,6 +37273,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E852" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F852" s="0" t="inlineStr">
         <is>
           <t>user-850@example.com</t>
@@ -37531,9 +37316,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E853" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F853" s="0" t="inlineStr">
         <is>
           <t>user-851@example.com</t>
@@ -37574,14 +37356,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D854" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E854" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F854" s="0" t="inlineStr">
         <is>
           <t>user-852@example.com</t>
@@ -37622,6 +37396,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D855" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E855" s="0">
         <v>24.4</v>
       </c>
@@ -37665,6 +37444,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E856" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F856" s="0" t="inlineStr">
         <is>
           <t>user-854@example.com</t>
@@ -37748,9 +37530,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E858" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F858" s="0" t="inlineStr">
         <is>
           <t>user-856@example.com</t>
@@ -37921,9 +37700,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E862" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F862" s="0" t="inlineStr">
         <is>
           <t>user-860@example.com</t>
@@ -37964,11 +37740,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D863" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E863" s="0">
         <v>24.4</v>
       </c>
@@ -38095,9 +37866,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E866" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F866" s="0" t="inlineStr">
         <is>
           <t>user-864@example.com</t>
@@ -38138,10 +37906,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D867" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E867" s="0">
+        <v>24.4</v>
       </c>
       <c r="F867" s="0" t="inlineStr">
         <is>
@@ -38188,6 +37954,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E868" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F868" s="0" t="inlineStr">
         <is>
           <t>user-866@example.com</t>
@@ -38228,6 +37997,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D869" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E869" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F869" s="0" t="inlineStr">
         <is>
           <t>user-867@example.com</t>
@@ -38268,11 +38045,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D870" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F870" s="0" t="inlineStr">
         <is>
           <t>user-868@example.com</t>
@@ -38313,14 +38085,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D871" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E871" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F871" s="0" t="inlineStr">
         <is>
           <t>user-869@example.com</t>
@@ -38361,11 +38125,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D872" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F872" s="0" t="inlineStr">
         <is>
           <t>user-870@example.com</t>
@@ -38406,6 +38165,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E873" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F873" s="0" t="inlineStr">
         <is>
           <t>user-871@example.com</t>
@@ -38446,10 +38208,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D874" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E874" s="0">
+        <v>24.4</v>
       </c>
       <c r="F874" s="0" t="inlineStr">
         <is>
@@ -38491,6 +38251,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D875" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E875" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F875" s="0" t="inlineStr">
         <is>
           <t>user-873@example.com</t>
@@ -38536,6 +38304,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E876" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F876" s="0" t="inlineStr">
         <is>
           <t>user-874@example.com</t>
@@ -38576,6 +38347,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D877" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E877" s="0">
         <v>24.4</v>
       </c>
@@ -38619,6 +38395,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D878" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E878" s="0">
         <v>24.4</v>
       </c>
@@ -38662,8 +38443,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E879" s="0">
-        <v>24.4</v>
+      <c r="D879" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F879" s="0" t="inlineStr">
         <is>
@@ -38710,6 +38493,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E880" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F880" s="0" t="inlineStr">
         <is>
           <t>user-878@example.com</t>
@@ -38750,6 +38536,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D881" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F881" s="0" t="inlineStr">
         <is>
           <t>user-879@example.com</t>
@@ -38790,11 +38581,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D882" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E882" s="0">
         <v>24.4</v>
       </c>
@@ -38838,9 +38624,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E883" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F883" s="0" t="inlineStr">
         <is>
           <t>user-881@example.com</t>
@@ -38881,6 +38664,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D884" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E884" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F884" s="0" t="inlineStr">
         <is>
           <t>user-882@example.com</t>
@@ -38921,14 +38712,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D885" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E885" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F885" s="0" t="inlineStr">
         <is>
           <t>user-883@example.com</t>
@@ -38974,9 +38757,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E886" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F886" s="0" t="inlineStr">
         <is>
           <t>user-884@example.com</t>
@@ -39017,6 +38797,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D887" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F887" s="0" t="inlineStr">
         <is>
           <t>user-885@example.com</t>
@@ -39057,6 +38842,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D888" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F888" s="0" t="inlineStr">
         <is>
           <t>user-886@example.com</t>
@@ -39097,9 +38887,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E889" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F889" s="0" t="inlineStr">
         <is>
           <t>user-887@example.com</t>
@@ -39140,6 +38927,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D890" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E890" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F890" s="0" t="inlineStr">
         <is>
           <t>user-888@example.com</t>
@@ -39185,6 +38980,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E891" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F891" s="0" t="inlineStr">
         <is>
           <t>user-889@example.com</t>
@@ -39230,9 +39028,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E892" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F892" s="0" t="inlineStr">
         <is>
           <t>user-890@example.com</t>
@@ -39273,10 +39068,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D893" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E893" s="0">
+        <v>24.4</v>
       </c>
       <c r="F893" s="0" t="inlineStr">
         <is>
@@ -39323,6 +39116,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E894" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F894" s="0" t="inlineStr">
         <is>
           <t>user-892@example.com</t>
@@ -39363,6 +39159,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D895" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F895" s="0" t="inlineStr">
         <is>
           <t>user-893@example.com</t>
@@ -39443,6 +39244,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D897" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F897" s="0" t="inlineStr">
         <is>
           <t>user-895@example.com</t>
@@ -39483,10 +39289,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D898" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E898" s="0">
+        <v>24.4</v>
       </c>
       <c r="F898" s="0" t="inlineStr">
         <is>
@@ -39576,11 +39380,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D900" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E900" s="0">
         <v>24.4</v>
       </c>
@@ -39672,14 +39471,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D902" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E902" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F902" s="0" t="inlineStr">
         <is>
           <t>user-900@example.com</t>
@@ -39720,6 +39511,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D903" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E903" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F903" s="0" t="inlineStr">
         <is>
           <t>user-901@example.com</t>
@@ -39760,11 +39559,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D904" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E904" s="0">
         <v>24.4</v>
       </c>
@@ -39808,11 +39602,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D905" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F905" s="0" t="inlineStr">
         <is>
           <t>user-903@example.com</t>
@@ -39853,6 +39642,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D906" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E906" s="0">
         <v>24.4</v>
       </c>
@@ -39992,6 +39786,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E909" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F909" s="0" t="inlineStr">
         <is>
           <t>user-907@example.com</t>
@@ -40085,9 +39882,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E911" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F911" s="0" t="inlineStr">
         <is>
           <t>user-909@example.com</t>
@@ -40128,10 +39922,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D912" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E912" s="0">
+        <v>24.4</v>
       </c>
       <c r="F912" s="0" t="inlineStr">
         <is>
@@ -40173,6 +39965,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D913" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E913" s="0">
         <v>24.4</v>
       </c>
@@ -40216,6 +40013,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D914" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E914" s="0">
         <v>24.4</v>
       </c>
@@ -40307,14 +40109,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D916" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E916" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F916" s="0" t="inlineStr">
         <is>
           <t>user-914@example.com</t>
@@ -40403,11 +40197,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D918" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E918" s="0">
         <v>24.4</v>
       </c>
@@ -40499,11 +40288,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D920" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F920" s="0" t="inlineStr">
         <is>
           <t>user-918@example.com</t>
@@ -40584,6 +40368,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E922" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F922" s="0" t="inlineStr">
         <is>
           <t>user-920@example.com</t>
@@ -40629,6 +40416,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E923" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F923" s="0" t="inlineStr">
         <is>
           <t>user-921@example.com</t>
@@ -40669,11 +40459,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D924" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F924" s="0" t="inlineStr">
         <is>
           <t>user-922@example.com</t>
@@ -40714,10 +40499,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D925" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E925" s="0">
+        <v>24.4</v>
       </c>
       <c r="F925" s="0" t="inlineStr">
         <is>
@@ -40759,6 +40542,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D926" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E926" s="0">
         <v>24.4</v>
       </c>
@@ -40802,11 +40590,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D927" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F927" s="0" t="inlineStr">
         <is>
           <t>user-925@example.com</t>
@@ -40847,11 +40630,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D928" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F928" s="0" t="inlineStr">
         <is>
           <t>user-926@example.com</t>
@@ -40975,6 +40753,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D931" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F931" s="0" t="inlineStr">
         <is>
           <t>user-929@example.com</t>
@@ -41020,9 +40803,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E932" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F932" s="0" t="inlineStr">
         <is>
           <t>user-930@example.com</t>
@@ -41063,6 +40843,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E933" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F933" s="0" t="inlineStr">
         <is>
           <t>user-931@example.com</t>
@@ -41189,6 +40972,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D936" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F936" s="0" t="inlineStr">
         <is>
           <t>user-934@example.com</t>
@@ -41229,6 +41017,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D937" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F937" s="0" t="inlineStr">
         <is>
           <t>user-935@example.com</t>
@@ -41269,10 +41062,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D938" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E938" s="0">
+        <v>24.4</v>
       </c>
       <c r="F938" s="0" t="inlineStr">
         <is>
@@ -41354,6 +41145,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E940" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F940" s="0" t="inlineStr">
         <is>
           <t>user-938@example.com</t>
@@ -41532,6 +41326,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E944" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F944" s="0" t="inlineStr">
         <is>
           <t>user-942@example.com</t>
@@ -41572,11 +41369,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D945" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E945" s="0">
         <v>24.4</v>
       </c>
@@ -41620,9 +41412,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E946" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F946" s="0" t="inlineStr">
         <is>
           <t>user-944@example.com</t>
@@ -41756,6 +41545,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E949" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F949" s="0" t="inlineStr">
         <is>
           <t>user-947@example.com</t>
@@ -41839,8 +41631,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E951" s="0">
-        <v>24.4</v>
+      <c r="D951" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F951" s="0" t="inlineStr">
         <is>
@@ -41882,14 +41676,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D952" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E952" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F952" s="0" t="inlineStr">
         <is>
           <t>user-950@example.com</t>
@@ -41930,10 +41716,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D953" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E953" s="0">
+        <v>24.4</v>
       </c>
       <c r="F953" s="0" t="inlineStr">
         <is>
@@ -42015,10 +41799,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D955" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E955" s="0">
+        <v>24.4</v>
       </c>
       <c r="F955" s="0" t="inlineStr">
         <is>
@@ -42108,8 +41890,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E957" s="0">
-        <v>24.4</v>
+      <c r="D957" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F957" s="0" t="inlineStr">
         <is>
@@ -42151,6 +41935,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D958" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E958" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F958" s="0" t="inlineStr">
         <is>
           <t>user-956@example.com</t>
@@ -42191,6 +41983,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D959" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F959" s="0" t="inlineStr">
         <is>
           <t>user-957@example.com</t>
@@ -42271,14 +42068,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D961" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E961" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F961" s="0" t="inlineStr">
         <is>
           <t>user-959@example.com</t>
@@ -42319,6 +42108,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D962" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E962" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F962" s="0" t="inlineStr">
         <is>
           <t>user-960@example.com</t>
@@ -42359,10 +42156,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D963" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E963" s="0">
+        <v>24.4</v>
       </c>
       <c r="F963" s="0" t="inlineStr">
         <is>
@@ -42404,9 +42199,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E964" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F964" s="0" t="inlineStr">
         <is>
           <t>user-962@example.com</t>
@@ -42447,6 +42239,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D965" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F965" s="0" t="inlineStr">
         <is>
           <t>user-963@example.com</t>
@@ -42535,9 +42332,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E967" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F967" s="0" t="inlineStr">
         <is>
           <t>user-965@example.com</t>
@@ -42621,8 +42415,10 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E969" s="0">
-        <v>24.4</v>
+      <c r="D969" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
       </c>
       <c r="F969" s="0" t="inlineStr">
         <is>
@@ -42664,6 +42460,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E970" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F970" s="0" t="inlineStr">
         <is>
           <t>user-968@example.com</t>
@@ -42709,9 +42508,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E971" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F971" s="0" t="inlineStr">
         <is>
           <t>user-969@example.com</t>
@@ -42752,9 +42548,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="E972" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F972" s="0" t="inlineStr">
         <is>
           <t>user-970@example.com</t>
@@ -42795,10 +42588,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D973" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E973" s="0">
+        <v>24.4</v>
       </c>
       <c r="F973" s="0" t="inlineStr">
         <is>
@@ -42845,6 +42636,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E974" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F974" s="0" t="inlineStr">
         <is>
           <t>user-972@example.com</t>
@@ -42930,6 +42724,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E976" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F976" s="0" t="inlineStr">
         <is>
           <t>user-974@example.com</t>
@@ -42970,14 +42767,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D977" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E977" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F977" s="0" t="inlineStr">
         <is>
           <t>user-975@example.com</t>
@@ -43018,6 +42807,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D978" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E978" s="0">
         <v>24.4</v>
       </c>
@@ -43061,6 +42855,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D979" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F979" s="0" t="inlineStr">
         <is>
           <t>user-977@example.com</t>
@@ -43101,14 +42900,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D980" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
-      <c r="E980" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F980" s="0" t="inlineStr">
         <is>
           <t>user-978@example.com</t>
@@ -43194,11 +42985,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D982" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="E982" s="0">
         <v>24.4</v>
       </c>
@@ -43242,6 +43028,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E983" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F983" s="0" t="inlineStr">
         <is>
           <t>user-981@example.com</t>
@@ -43282,6 +43071,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D984" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E984" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F984" s="0" t="inlineStr">
         <is>
           <t>user-982@example.com</t>
@@ -43322,10 +43119,8 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D985" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
+      <c r="E985" s="0">
+        <v>24.4</v>
       </c>
       <c r="F985" s="0" t="inlineStr">
         <is>
@@ -43367,6 +43162,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D986" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="F986" s="0" t="inlineStr">
         <is>
           <t>user-984@example.com</t>
@@ -43412,6 +43212,9 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
+      <c r="E987" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F987" s="0" t="inlineStr">
         <is>
           <t>user-985@example.com</t>
@@ -43452,6 +43255,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D988" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E988" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F988" s="0" t="inlineStr">
         <is>
           <t>user-986@example.com</t>
@@ -43535,11 +43346,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D990" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F990" s="0" t="inlineStr">
         <is>
           <t>user-988@example.com</t>
@@ -43580,6 +43386,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D991" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E991" s="0">
         <v>24.4</v>
       </c>
@@ -43623,6 +43434,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E992" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F992" s="0" t="inlineStr">
         <is>
           <t>user-990@example.com</t>
@@ -43708,11 +43522,6 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
-      <c r="D994" s="0" t="inlineStr">
-        <is>
-          <t>2025-01-01 12:10:00</t>
-        </is>
-      </c>
       <c r="F994" s="0" t="inlineStr">
         <is>
           <t>user-992@example.com</t>
@@ -43798,9 +43607,6 @@
           <t>2025-01-01 12:10:00</t>
         </is>
       </c>
-      <c r="E996" s="0">
-        <v>24.4</v>
-      </c>
       <c r="F996" s="0" t="inlineStr">
         <is>
           <t>user-994@example.com</t>
@@ -43841,6 +43647,11 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D997" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
       <c r="E997" s="0">
         <v>24.4</v>
       </c>
@@ -43884,6 +43695,9 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="E998" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F998" s="0" t="inlineStr">
         <is>
           <t>user-996@example.com</t>
@@ -43924,6 +43738,14 @@
           <t>2025-01-01 12:00:00</t>
         </is>
       </c>
+      <c r="D999" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 12:10:00</t>
+        </is>
+      </c>
+      <c r="E999" s="0">
+        <v>24.4</v>
+      </c>
       <c r="F999" s="0" t="inlineStr">
         <is>
           <t>user-997@example.com</t>
@@ -44011,6 +43833,9 @@
         <is>
           <t>2025-01-01 12:10:00</t>
         </is>
+      </c>
+      <c r="E1001" s="0">
+        <v>24.4</v>
       </c>
       <c r="F1001" s="0" t="inlineStr">
         <is>
